--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G8">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G9">

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G4">

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G5">

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G3">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G4">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G5">

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q5">
         <v>0</v>

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q2">
         <v>0</v>

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="O2">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="P2">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="O3">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="P3">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -961,13 +961,13 @@
         </is>
       </c>
       <c r="N4">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="O4">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>6.75</v>
+        <v>6.7</v>
       </c>
       <c r="O5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="P5">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q5">
         <v>0</v>

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-08-12 19:00:00</t>
+          <t>2026-08-12 16:00:00</t>
         </is>
       </c>
     </row>

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -644,55 +644,55 @@
         <v>2.72</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="O3">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="P3">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -970,55 +970,55 @@
         <v>2.78</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1133,55 +1133,55 @@
         <v>1.5</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U5">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>0</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC7">
         <v>0</v>
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AL9">
         <v>0</v>

--- a/jogos_2026-08-12.xlsx
+++ b/jogos_2026-08-12.xlsx
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="O2">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="P2">
-        <v>2.72</v>
+        <v>2.55</v>
       </c>
       <c r="Q2">
         <v>3.72</v>
@@ -674,19 +674,19 @@
         <v>2.39</v>
       </c>
       <c r="AA2">
-        <v>2.52</v>
+        <v>2.7</v>
       </c>
       <c r="AB2">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AC2">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AD2">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AE2">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF2">
         <v>2.09</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Durban City</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.8</v>
+        <v>2.57</v>
       </c>
       <c r="O3">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P3">
-        <v>4.4</v>
+        <v>2.94</v>
       </c>
       <c r="Q3">
-        <v>2.49</v>
+        <v>3.38</v>
       </c>
       <c r="R3">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="S3">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="T3">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="U3">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="V3">
         <v>1.22</v>
       </c>
       <c r="W3">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3">
         <v>1.08</v>
       </c>
       <c r="Y3">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Z3">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="AA3">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="AB3">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AC3">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AD3">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="AG3">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AK3">
-        <v>1.83</v>
+        <v>1.44</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Durban City</t>
+          <t>AmaZulu</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Orlando Pirates</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
+        <v>5.93</v>
+      </c>
+      <c r="O4">
+        <v>3.6</v>
+      </c>
+      <c r="P4">
+        <v>1.53</v>
+      </c>
+      <c r="Q4">
+        <v>6.45</v>
+      </c>
+      <c r="R4">
+        <v>2.17</v>
+      </c>
+      <c r="S4">
+        <v>1.44</v>
+      </c>
+      <c r="T4">
         <v>2.48</v>
       </c>
-      <c r="O4">
-        <v>3</v>
-      </c>
-      <c r="P4">
-        <v>2.78</v>
-      </c>
-      <c r="Q4">
-        <v>3.38</v>
-      </c>
-      <c r="R4">
-        <v>1.89</v>
-      </c>
-      <c r="S4">
-        <v>1.61</v>
-      </c>
-      <c r="T4">
-        <v>2.25</v>
-      </c>
       <c r="U4">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="V4">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
         <v>1.02</v>
       </c>
       <c r="X4">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y4">
-        <v>1.55</v>
+        <v>1.34</v>
       </c>
       <c r="Z4">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="AA4">
-        <v>2.77</v>
+        <v>2.15</v>
       </c>
       <c r="AB4">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="AC4">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AD4">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AG4">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="AK4">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AmaZulu</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orlando Pirates</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="G5">
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>6.7</v>
+        <v>1.78</v>
       </c>
       <c r="O5">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="P5">
+        <v>4.64</v>
+      </c>
+      <c r="Q5">
+        <v>2.4</v>
+      </c>
+      <c r="R5">
+        <v>2</v>
+      </c>
+      <c r="S5">
+        <v>1.55</v>
+      </c>
+      <c r="T5">
+        <v>2.25</v>
+      </c>
+      <c r="U5">
+        <v>3.7</v>
+      </c>
+      <c r="V5">
+        <v>1.22</v>
+      </c>
+      <c r="W5">
+        <v>1.01</v>
+      </c>
+      <c r="X5">
+        <v>1.1</v>
+      </c>
+      <c r="Y5">
         <v>1.5</v>
       </c>
-      <c r="Q5">
-        <v>6.45</v>
-      </c>
-      <c r="R5">
-        <v>2.17</v>
-      </c>
-      <c r="S5">
-        <v>1.44</v>
-      </c>
-      <c r="T5">
-        <v>2.48</v>
-      </c>
-      <c r="U5">
-        <v>3.02</v>
-      </c>
-      <c r="V5">
-        <v>1.31</v>
-      </c>
-      <c r="W5">
-        <v>1.02</v>
-      </c>
-      <c r="X5">
-        <v>1.04</v>
-      </c>
-      <c r="Y5">
-        <v>1.39</v>
-      </c>
       <c r="Z5">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="AA5">
-        <v>2.19</v>
+        <v>2.56</v>
       </c>
       <c r="AB5">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="AC5">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AD5">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="AE5">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AF5">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AG5">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="AK5">
-        <v>1.13</v>
+        <v>1.96</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Santiago Wanderers</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="P8">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="Q8">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="R8">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="S8">
-        <v>1.33</v>
+        <v>1.39</v>
       </c>
       <c r="T8">
-        <v>2.91</v>
+        <v>2.66</v>
       </c>
       <c r="U8">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="V8">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1</v>
       </c>
       <c r="Y8">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z8">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="AA8">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AB8">
-        <v>1.96</v>
+        <v>1.77</v>
       </c>
       <c r="AC8">
-        <v>2.78</v>
+        <v>3.34</v>
       </c>
       <c r="AD8">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AE8">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF8">
-        <v>1.66</v>
+        <v>2</v>
       </c>
       <c r="AG8">
-        <v>2.07</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK8">
-        <v>1.81</v>
+        <v>2.2</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Santiago Wanderers</t>
         </is>
       </c>
       <c r="G9">
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O9">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="P9">
-        <v>5.25</v>
+        <v>3.2</v>
       </c>
       <c r="Q9">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="R9">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="S9">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="T9">
-        <v>2.66</v>
+        <v>2.91</v>
       </c>
       <c r="U9">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="V9">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
         <v>1</v>
       </c>
       <c r="Y9">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z9">
-        <v>3.14</v>
+        <v>3.9</v>
       </c>
       <c r="AA9">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AB9">
-        <v>1.77</v>
+        <v>1.96</v>
       </c>
       <c r="AC9">
-        <v>3.34</v>
+        <v>2.78</v>
       </c>
       <c r="AD9">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AE9">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF9">
-        <v>2</v>
+        <v>1.66</v>
       </c>
       <c r="AG9">
-        <v>1.73</v>
+        <v>2.07</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK9">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="AL9">
         <v>0</v>
